--- a/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -495,61 +495,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9598981736089301</v>
+        <v>0.9596975999639462</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009749228207078111</v>
+        <v>0.0009939481099400654</v>
       </c>
       <c r="F2" t="n">
-        <v>1.748860356875015e-06</v>
+        <v>1.757607472104272e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001322444840768421</v>
+        <v>0.001325747891608458</v>
       </c>
       <c r="H2" t="n">
-        <v>183.0815975457437</v>
+        <v>204.4001926443917</v>
       </c>
       <c r="I2" t="n">
-        <v>-663.3404027541497</v>
+        <v>-661.0809673578487</v>
       </c>
       <c r="J2" t="n">
-        <v>-637.9742344125912</v>
+        <v>-633.7635552977088</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>P, mu, dXdt, dVdt, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9596975999639462</v>
+        <v>0.9561088077284187</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009939481099400654</v>
+        <v>0.001068765942141017</v>
       </c>
       <c r="F3" t="n">
-        <v>1.757607472104272e-06</v>
+        <v>1.914116465200221e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001325747891608458</v>
+        <v>0.001383515979380152</v>
       </c>
       <c r="H3" t="n">
-        <v>204.4001926443917</v>
+        <v>281.0472406681561</v>
       </c>
       <c r="I3" t="n">
-        <v>-663.0809673578487</v>
+        <v>-668.6452297189867</v>
       </c>
       <c r="J3" t="n">
-        <v>-637.7147990162902</v>
+        <v>-653.0352799703353</v>
       </c>
     </row>
     <row r="4">
@@ -582,10 +582,10 @@
         <v>718.1684751958879</v>
       </c>
       <c r="I4" t="n">
-        <v>-591.1153749654535</v>
+        <v>-589.1153749654535</v>
       </c>
       <c r="J4" t="n">
-        <v>-563.7979629053135</v>
+        <v>-559.8467191867321</v>
       </c>
     </row>
     <row r="5">
@@ -603,25 +603,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7707615440405245</v>
+        <v>0.7707615942592828</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00143987873727133</v>
+        <v>0.001439878574136392</v>
       </c>
       <c r="F5" t="n">
-        <v>9.997201723162465e-06</v>
+        <v>9.997199533097736e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003161835182795344</v>
+        <v>0.003161834836467227</v>
       </c>
       <c r="H5" t="n">
-        <v>144.5052854089966</v>
+        <v>144.5057529125964</v>
       </c>
       <c r="I5" t="n">
-        <v>-588.6866772542787</v>
+        <v>-588.6866886458042</v>
       </c>
       <c r="J5" t="n">
-        <v>-578.9304586613716</v>
+        <v>-578.9304700528971</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +639,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7337613687498108</v>
+        <v>0.7342428403908046</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002167076391859498</v>
+        <v>0.002349103548185343</v>
       </c>
       <c r="F6" t="n">
-        <v>1.161079755125087e-05</v>
+        <v>1.158980033636888e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003407462039590592</v>
+        <v>0.003404379581710723</v>
       </c>
       <c r="H6" t="n">
-        <v>618.5955887673789</v>
+        <v>772.4941915464079</v>
       </c>
       <c r="I6" t="n">
-        <v>-560.9059036096164</v>
+        <v>-559.0000266556912</v>
       </c>
       <c r="J6" t="n">
-        <v>-531.637247830895</v>
+        <v>-527.7801271583883</v>
       </c>
     </row>
     <row r="7">
@@ -690,10 +690,10 @@
         <v>1416.545716351248</v>
       </c>
       <c r="I7" t="n">
-        <v>-559.968804354619</v>
+        <v>-557.968804354619</v>
       </c>
       <c r="J7" t="n">
-        <v>-532.651392294479</v>
+        <v>-528.7001485758976</v>
       </c>
     </row>
     <row r="8">
@@ -711,25 +711,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02406435455150846</v>
+        <v>-0.02406419988102071</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005990156174651198</v>
+        <v>0.005990155701349769</v>
       </c>
       <c r="F8" t="n">
-        <v>4.465994977632123e-05</v>
+        <v>4.465994303106524e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006682810020965824</v>
+        <v>0.006682809516293671</v>
       </c>
       <c r="H8" t="n">
-        <v>3587.857791778035</v>
+        <v>3587.855975873948</v>
       </c>
       <c r="I8" t="n">
-        <v>-510.854538678836</v>
+        <v>-510.8545465327037</v>
       </c>
       <c r="J8" t="n">
-        <v>-501.0983200859288</v>
+        <v>-501.0983279397965</v>
       </c>
     </row>
     <row r="9">
@@ -762,10 +762,10 @@
         <v>4082.887148907911</v>
       </c>
       <c r="I9" t="n">
-        <v>-488.0832422522421</v>
+        <v>-486.0832422522421</v>
       </c>
       <c r="J9" t="n">
-        <v>-460.7658301921022</v>
+        <v>-456.8145864735208</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.5748618730590263</v>
+        <v>-0.5748623049414729</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007836091265545814</v>
+        <v>0.007836092369424275</v>
       </c>
       <c r="F10" t="n">
-        <v>6.868050024674661e-05</v>
+        <v>6.868051908135236e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008287369923368126</v>
+        <v>0.008287371059712022</v>
       </c>
       <c r="H10" t="n">
-        <v>4459.762088897917</v>
+        <v>4459.762320966935</v>
       </c>
       <c r="I10" t="n">
-        <v>-488.4743523879105</v>
+        <v>-488.4743381276858</v>
       </c>
       <c r="J10" t="n">
-        <v>-478.7181337950033</v>
+        <v>-478.7181195347787</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -495,25 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9596975999639462</v>
+        <v>0.9596975485858285</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009939481099400654</v>
+        <v>0.0009939486313763532</v>
       </c>
       <c r="F2" t="n">
-        <v>1.757607472104272e-06</v>
+        <v>1.757609494474204e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001325747891608458</v>
+        <v>0.001325748654336184</v>
       </c>
       <c r="H2" t="n">
-        <v>204.4001926443917</v>
+        <v>865815.2097739427</v>
       </c>
       <c r="I2" t="n">
-        <v>-661.0809673578487</v>
+        <v>0.0135919657508976</v>
       </c>
       <c r="J2" t="n">
-        <v>-633.7635552977088</v>
+        <v>-683.0809075247075</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-677.2271763689632</v>
       </c>
     </row>
     <row r="3">
@@ -523,33 +531,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, mu, dXdt, dVdt, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9561088077284187</v>
+        <v>0.9558307428663747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001068765942141017</v>
+        <v>0.0010041817023292</v>
       </c>
       <c r="F3" t="n">
-        <v>1.914116465200221e-06</v>
+        <v>1.926242771292921e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001383515979380152</v>
+        <v>0.001387891483975934</v>
       </c>
       <c r="H3" t="n">
-        <v>281.0472406681561</v>
+        <v>702025.3213993447</v>
       </c>
       <c r="I3" t="n">
-        <v>-668.6452297189867</v>
+        <v>0.0142521255100275</v>
       </c>
       <c r="J3" t="n">
-        <v>-653.0352799703353</v>
+        <v>-680.3168385588493</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-676.4143511216864</v>
       </c>
     </row>
     <row r="4">
@@ -567,25 +578,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8452357203650598</v>
+        <v>0.845235615886665</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001625688661816988</v>
+        <v>0.001625688950634662</v>
       </c>
       <c r="F4" t="n">
-        <v>6.74934629346804e-06</v>
+        <v>6.749350011706765e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002597950402426505</v>
+        <v>0.002597951118036435</v>
       </c>
       <c r="H4" t="n">
-        <v>718.1684751958879</v>
+        <v>1334215.537614396</v>
       </c>
       <c r="I4" t="n">
-        <v>-589.1153749654535</v>
+        <v>0.04743403977900872</v>
       </c>
       <c r="J4" t="n">
-        <v>-559.8467191867321</v>
+        <v>-615.1153463184776</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-611.2128588813147</v>
       </c>
     </row>
     <row r="5">
@@ -595,33 +609,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, dVdt, Plag1, X_calc, V_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7707615942592828</v>
+        <v>0.7669122545571241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001439878574136392</v>
+        <v>0.002147136267858614</v>
       </c>
       <c r="F5" t="n">
-        <v>9.997199533097736e-06</v>
+        <v>1.016506986698903e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003161834836467227</v>
+        <v>0.003188270670283347</v>
       </c>
       <c r="H5" t="n">
-        <v>144.5057529125964</v>
+        <v>1257276.617252152</v>
       </c>
       <c r="I5" t="n">
-        <v>-588.6866886458042</v>
+        <v>0.07043343918176968</v>
       </c>
       <c r="J5" t="n">
-        <v>-578.9304700528971</v>
+        <v>-595.820768356134</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-593.8695246375526</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7342428403908046</v>
+        <v>0.7609669952074398</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002349103548185343</v>
+        <v>0.002106356405827263</v>
       </c>
       <c r="F6" t="n">
-        <v>1.158980033636888e-05</v>
+        <v>1.042434551681816e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003404379581710723</v>
+        <v>0.003228675505035798</v>
       </c>
       <c r="H6" t="n">
-        <v>772.4941915464079</v>
+        <v>1261210.114884991</v>
       </c>
       <c r="I6" t="n">
-        <v>-559.0000266556912</v>
+        <v>0.07221719847962983</v>
       </c>
       <c r="J6" t="n">
-        <v>-527.7801271583883</v>
+        <v>-594.5110617653976</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-592.5598180468162</v>
       </c>
     </row>
     <row r="7">
@@ -667,75 +687,81 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, dXdt</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7182906982024128</v>
+        <v>0.7125485908906762</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002562626106463156</v>
+        <v>0.002621422764926403</v>
       </c>
       <c r="F7" t="n">
-        <v>1.228548109685226e-05</v>
+        <v>1.253589566199148e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003505065063141091</v>
+        <v>0.003540606679933748</v>
       </c>
       <c r="H7" t="n">
-        <v>1416.545716351248</v>
+        <v>2037955.527343165</v>
       </c>
       <c r="I7" t="n">
-        <v>-557.968804354619</v>
+        <v>0.08674419785976055</v>
       </c>
       <c r="J7" t="n">
-        <v>-528.7001485758976</v>
+        <v>-584.9195475528024</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-582.968303834221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V, P, dVdt, Plag1, X_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02406419988102071</v>
+        <v>-0.1224765471077778</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005990155701349769</v>
+        <v>0.006309897036567106</v>
       </c>
       <c r="F8" t="n">
-        <v>4.465994303106524e-05</v>
+        <v>4.895174777947941e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006682809516293671</v>
+        <v>0.006996552563904555</v>
       </c>
       <c r="H8" t="n">
-        <v>3587.855975873948</v>
+        <v>6442700.266205044</v>
       </c>
       <c r="I8" t="n">
-        <v>-510.8545465327037</v>
+        <v>0.6755544607115581</v>
       </c>
       <c r="J8" t="n">
-        <v>-501.0983279397965</v>
+        <v>-512.0831251795505</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-508.1806377423877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -747,25 +773,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1224738805835961</v>
+        <v>-0.1316396250001863</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00630988724601267</v>
+        <v>0.006353609567003881</v>
       </c>
       <c r="F9" t="n">
-        <v>4.895163756974061e-05</v>
+        <v>4.935135405992122e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006996544687897063</v>
+        <v>0.007025051890194208</v>
       </c>
       <c r="H9" t="n">
-        <v>4082.887148907911</v>
+        <v>6463097.719772712</v>
       </c>
       <c r="I9" t="n">
-        <v>-486.0832422522421</v>
+        <v>0.6810528668957958</v>
       </c>
       <c r="J9" t="n">
-        <v>-456.8145864735208</v>
+        <v>-511.6603584376497</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-507.7578710004869</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V, P, dVdt, Plag1, X_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.5748623049414729</v>
+        <v>-0.6632445656812951</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007836092369424275</v>
+        <v>0.008005232912943137</v>
       </c>
       <c r="F10" t="n">
-        <v>6.868051908135236e-05</v>
+        <v>7.25349039003154e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008287371059712022</v>
+        <v>0.008516742563933432</v>
       </c>
       <c r="H10" t="n">
-        <v>4459.762320966935</v>
+        <v>7444784.507490601</v>
       </c>
       <c r="I10" t="n">
-        <v>-488.4743381276858</v>
+        <v>0.9990482882742376</v>
       </c>
       <c r="J10" t="n">
-        <v>-478.7181195347787</v>
+        <v>-493.6350193000743</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-491.6837755814929</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
@@ -488,40 +488,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9596975485858285</v>
+        <v>0.4627064212682644</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009939486313763532</v>
+        <v>0.002422739537039809</v>
       </c>
       <c r="F2" t="n">
-        <v>1.757609494474204e-06</v>
+        <v>2.343163702031997e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001325748654336184</v>
+        <v>0.004840623618948283</v>
       </c>
       <c r="H2" t="n">
-        <v>865815.2097739427</v>
+        <v>213.1504797125515</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0135919657508976</v>
+        <v>0.1622044757654349</v>
       </c>
       <c r="J2" t="n">
-        <v>-683.0809075247075</v>
+        <v>-550.3940188450043</v>
       </c>
       <c r="K2" t="n">
-        <v>-677.2271763689632</v>
+        <v>-546.4915314078414</v>
       </c>
     </row>
     <row r="3">
@@ -535,77 +535,77 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>X_calc, V_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9558307428663747</v>
+        <v>0.3071127627657998</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0010041817023292</v>
+        <v>0.002915685086294604</v>
       </c>
       <c r="F3" t="n">
-        <v>1.926242771292921e-06</v>
+        <v>3.02171529337973e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001387891483975934</v>
+        <v>0.005497013092016181</v>
       </c>
       <c r="H3" t="n">
-        <v>702025.3213993447</v>
+        <v>313.8210717097527</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0142521255100275</v>
+        <v>0.2088873231773138</v>
       </c>
       <c r="J3" t="n">
-        <v>-680.3168385588493</v>
+        <v>-537.1692424778412</v>
       </c>
       <c r="K3" t="n">
-        <v>-676.4143511216864</v>
+        <v>-533.2667550406783</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>V_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.845235615886665</v>
+        <v>-0.01851942296210818</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001625688950634662</v>
+        <v>0.005413759437865609</v>
       </c>
       <c r="F4" t="n">
-        <v>6.749350011706765e-06</v>
+        <v>4.44181325846622e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002597951118036435</v>
+        <v>0.006664692985026558</v>
       </c>
       <c r="H4" t="n">
-        <v>1334215.537614396</v>
+        <v>1174.213834734979</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04743403977900872</v>
+        <v>0.6141738391628835</v>
       </c>
       <c r="J4" t="n">
-        <v>-615.1153463184776</v>
+        <v>-515.1368645781365</v>
       </c>
       <c r="K4" t="n">
-        <v>-611.2128588813147</v>
+        <v>-509.2831334223922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,38 +613,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7669122545571241</v>
+        <v>-0.1320537375607578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002147136267858614</v>
+        <v>0.003996194976914207</v>
       </c>
       <c r="F5" t="n">
-        <v>1.016506986698903e-05</v>
+        <v>4.936941984051573e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003188270670283347</v>
+        <v>0.007026337583728505</v>
       </c>
       <c r="H5" t="n">
-        <v>1257276.617252152</v>
+        <v>1527.787312332473</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07043343918176968</v>
+        <v>0.6803013597242314</v>
       </c>
       <c r="J5" t="n">
-        <v>-595.820768356134</v>
+        <v>-513.6413265649388</v>
       </c>
       <c r="K5" t="n">
-        <v>-593.8695246375526</v>
+        <v>-511.6900828463574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,32 +652,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7609669952074398</v>
+        <v>-0.1320537375607578</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002106356405827263</v>
+        <v>0.003996194976914207</v>
       </c>
       <c r="F6" t="n">
-        <v>1.042434551681816e-05</v>
+        <v>4.936941984051573e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003228675505035798</v>
+        <v>0.007026337583728505</v>
       </c>
       <c r="H6" t="n">
-        <v>1261210.114884991</v>
+        <v>1527.787312332473</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07221719847962983</v>
+        <v>0.6803013597242314</v>
       </c>
       <c r="J6" t="n">
-        <v>-594.5110617653976</v>
+        <v>-513.6413265649388</v>
       </c>
       <c r="K6" t="n">
-        <v>-592.5598180468162</v>
+        <v>-511.6900828463574</v>
       </c>
     </row>
     <row r="7">
@@ -691,38 +691,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7125485908906762</v>
+        <v>-0.1610258078543785</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002621422764926403</v>
+        <v>0.004141758130783618</v>
       </c>
       <c r="F7" t="n">
-        <v>1.253589566199148e-05</v>
+        <v>5.063290606428514e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003540606679933748</v>
+        <v>0.007115680295255341</v>
       </c>
       <c r="H7" t="n">
-        <v>2037955.527343165</v>
+        <v>1678.190593803374</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08674419785976055</v>
+        <v>0.6976863707811173</v>
       </c>
       <c r="J7" t="n">
-        <v>-584.9195475528024</v>
+        <v>-512.3272615291014</v>
       </c>
       <c r="K7" t="n">
-        <v>-582.968303834221</v>
+        <v>-510.37601781052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -730,77 +730,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, mu_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1224765471077778</v>
+        <v>-0.3684026555975792</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006309897036567106</v>
+        <v>0.003848767405471784</v>
       </c>
       <c r="F8" t="n">
-        <v>4.895174777947941e-05</v>
+        <v>5.967671230929328e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006996552563904555</v>
+        <v>0.007725070375685472</v>
       </c>
       <c r="H8" t="n">
-        <v>6442700.266205044</v>
+        <v>1015.848275251879</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6755544607115581</v>
+        <v>0.8231251407557807</v>
       </c>
       <c r="J8" t="n">
-        <v>-512.0831251795505</v>
+        <v>-501.7815719963477</v>
       </c>
       <c r="K8" t="n">
-        <v>-508.1806377423877</v>
+        <v>-497.8790845591848</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>V_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1316396250001863</v>
+        <v>-0.6598918628640473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006353609567003881</v>
+        <v>0.007866367541695226</v>
       </c>
       <c r="F9" t="n">
-        <v>4.935135405992122e-05</v>
+        <v>7.238869988995795e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007025051890194208</v>
+        <v>0.008508154905145882</v>
       </c>
       <c r="H9" t="n">
-        <v>6463097.719772712</v>
+        <v>4149.87773284071</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6810528668957958</v>
+        <v>0.9970364618982746</v>
       </c>
       <c r="J9" t="n">
-        <v>-511.6603584376497</v>
+        <v>-493.7399381803525</v>
       </c>
       <c r="K9" t="n">
-        <v>-507.7578710004869</v>
+        <v>-491.788694461771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.6632445656812951</v>
+        <v>-0.8828796361514863</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008005232912943137</v>
+        <v>0.008504081602618915</v>
       </c>
       <c r="F10" t="n">
-        <v>7.25349039003154e-05</v>
+        <v>8.21133062699077e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008516742563933432</v>
+        <v>0.009061639270568416</v>
       </c>
       <c r="H10" t="n">
-        <v>7444784.507490601</v>
+        <v>4858.091154423014</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9990482882742376</v>
+        <v>1.13084274031967</v>
       </c>
       <c r="J10" t="n">
-        <v>-493.6350193000743</v>
+        <v>-487.1853449966782</v>
       </c>
       <c r="K10" t="n">
-        <v>-491.6837755814929</v>
+        <v>-485.2341012780967</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
@@ -500,28 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4627064212682644</v>
+        <v>0.4608456715159602</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002422739537039809</v>
+        <v>0.002388826123049708</v>
       </c>
       <c r="F2" t="n">
-        <v>2.343163702031997e-05</v>
+        <v>2.268313310873223e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004840623618948283</v>
+        <v>0.004762681294054037</v>
       </c>
       <c r="H2" t="n">
-        <v>213.1504797125515</v>
+        <v>206.5885974303978</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1622044757654349</v>
+        <v>0.1627621767383881</v>
       </c>
       <c r="J2" t="n">
-        <v>-550.3940188450043</v>
+        <v>-573.4700030041744</v>
       </c>
       <c r="K2" t="n">
-        <v>-546.4915314078414</v>
+        <v>-569.4920349110458</v>
       </c>
     </row>
     <row r="3">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3071127627657998</v>
+        <v>0.3109215923320096</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002915685086294604</v>
+        <v>0.002823068040077226</v>
       </c>
       <c r="F3" t="n">
-        <v>3.02171529337973e-05</v>
+        <v>2.899069230777581e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005497013092016181</v>
+        <v>0.005384300540253656</v>
       </c>
       <c r="H3" t="n">
-        <v>313.8210717097527</v>
+        <v>308.2023884397309</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2088873231773138</v>
+        <v>0.2077438157850126</v>
       </c>
       <c r="J3" t="n">
-        <v>-537.1692424778412</v>
+        <v>-560.2209296575531</v>
       </c>
       <c r="K3" t="n">
-        <v>-533.2667550406783</v>
+        <v>-556.2429615644246</v>
       </c>
     </row>
     <row r="4">
@@ -578,28 +578,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01851942296210818</v>
+        <v>-0.0647247395407442</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005413759437865609</v>
+        <v>0.005475839905176957</v>
       </c>
       <c r="F4" t="n">
-        <v>4.44181325846622e-05</v>
+        <v>4.479476787114006e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006664692985026558</v>
+        <v>0.006692889351478931</v>
       </c>
       <c r="H4" t="n">
-        <v>1174.213834734979</v>
+        <v>1088.039139078064</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6141738391628835</v>
+        <v>0.6418975563994662</v>
       </c>
       <c r="J4" t="n">
-        <v>-515.1368645781365</v>
+        <v>-534.724637553531</v>
       </c>
       <c r="K4" t="n">
-        <v>-509.2831334223922</v>
+        <v>-528.7576854138382</v>
       </c>
     </row>
     <row r="5">
@@ -613,32 +613,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>dVdt_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1320537375607578</v>
+        <v>-0.1288552148376154</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003996194976914207</v>
+        <v>0.003874259614073351</v>
       </c>
       <c r="F5" t="n">
-        <v>4.936941984051573e-05</v>
+        <v>4.749284526871076e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007026337583728505</v>
+        <v>0.006891505297735086</v>
       </c>
       <c r="H5" t="n">
-        <v>1527.787312332473</v>
+        <v>1457.823911086033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6803013597242314</v>
+        <v>0.6783796188859456</v>
       </c>
       <c r="J5" t="n">
-        <v>-513.6413265649388</v>
+        <v>-535.5663001463022</v>
       </c>
       <c r="K5" t="n">
-        <v>-511.6900828463574</v>
+        <v>-533.5773160997379</v>
       </c>
     </row>
     <row r="6">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1320537375607578</v>
+        <v>-0.1288552148376154</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003996194976914207</v>
+        <v>0.003874259614073351</v>
       </c>
       <c r="F6" t="n">
-        <v>4.936941984051573e-05</v>
+        <v>4.749284526871076e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007026337583728505</v>
+        <v>0.006891505297735086</v>
       </c>
       <c r="H6" t="n">
-        <v>1527.787312332473</v>
+        <v>1457.823911086033</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6803013597242314</v>
+        <v>0.6783796188859456</v>
       </c>
       <c r="J6" t="n">
-        <v>-513.6413265649388</v>
+        <v>-535.5663001463022</v>
       </c>
       <c r="K6" t="n">
-        <v>-511.6900828463574</v>
+        <v>-533.5773160997379</v>
       </c>
     </row>
     <row r="7">
@@ -695,28 +695,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.1610258078543785</v>
+        <v>-0.1613771854246493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004141758130783618</v>
+        <v>0.00406390988750481</v>
       </c>
       <c r="F7" t="n">
-        <v>5.063290606428514e-05</v>
+        <v>4.886109949354131e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007115680295255341</v>
+        <v>0.006990071494165228</v>
       </c>
       <c r="H7" t="n">
-        <v>1678.190593803374</v>
+        <v>1590.227412921097</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6976863707811173</v>
+        <v>0.6978947167940807</v>
       </c>
       <c r="J7" t="n">
-        <v>-512.3272615291014</v>
+        <v>-534.0325654303032</v>
       </c>
       <c r="K7" t="n">
-        <v>-510.37601781052</v>
+        <v>-532.0435813837389</v>
       </c>
     </row>
     <row r="8">
@@ -734,28 +734,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.3684026555975792</v>
+        <v>-0.3518201161660621</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003848767405471784</v>
+        <v>0.003676107089678999</v>
       </c>
       <c r="F8" t="n">
-        <v>5.967671230929328e-05</v>
+        <v>5.687335520476002e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007725070375685472</v>
+        <v>0.007541442514848205</v>
       </c>
       <c r="H8" t="n">
-        <v>1015.848275251879</v>
+        <v>877.6800461580765</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8231251407557807</v>
+        <v>0.8131716923969241</v>
       </c>
       <c r="J8" t="n">
-        <v>-501.7815719963477</v>
+        <v>-523.8329144317564</v>
       </c>
       <c r="K8" t="n">
-        <v>-497.8790845591848</v>
+        <v>-519.8549463386279</v>
       </c>
     </row>
     <row r="9">
@@ -765,36 +765,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>V_calc</t>
+          <t>T, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.6598918628640473</v>
+        <v>-0.4201383808407051</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007866367541695226</v>
+        <v>0.006024469998403748</v>
       </c>
       <c r="F9" t="n">
-        <v>7.238869988995795e-05</v>
+        <v>5.974761997368027e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008508154905145882</v>
+        <v>0.007729658464232444</v>
       </c>
       <c r="H9" t="n">
-        <v>4149.87773284071</v>
+        <v>3291.357198646209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9970364618982746</v>
+        <v>0.8561666751723863</v>
       </c>
       <c r="J9" t="n">
-        <v>-493.7399381803525</v>
+        <v>-517.1705848552147</v>
       </c>
       <c r="K9" t="n">
-        <v>-491.788694461771</v>
+        <v>-509.2146486689576</v>
       </c>
     </row>
     <row r="10">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.8828796361514863</v>
+        <v>-0.4720797138620128</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008504081602618915</v>
+        <v>0.006267901696259799</v>
       </c>
       <c r="F10" t="n">
-        <v>8.21133062699077e-05</v>
+        <v>6.193287957102055e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009061639270568416</v>
+        <v>0.007869744568346583</v>
       </c>
       <c r="H10" t="n">
-        <v>4858.091154423014</v>
+        <v>1287.834068632945</v>
       </c>
       <c r="I10" t="n">
-        <v>1.13084274031967</v>
+        <v>0.8883345343486072</v>
       </c>
       <c r="J10" t="n">
-        <v>-487.1853449966782</v>
+        <v>-513.2308047328461</v>
       </c>
       <c r="K10" t="n">
-        <v>-485.2341012780967</v>
+        <v>-503.2858845000247</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,38 +496,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4608456715159602</v>
+        <v>0.9558307868926454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002388826123049708</v>
+        <v>0.001004181360587197</v>
       </c>
       <c r="F2" t="n">
-        <v>2.268313310873223e-05</v>
+        <v>1.926241090481066e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004762681294054037</v>
+        <v>0.001387890878448686</v>
       </c>
       <c r="H2" t="n">
-        <v>206.5885974303978</v>
+        <v>232.4792007485201</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1627621767383881</v>
+        <v>0.0142521123009697</v>
       </c>
       <c r="J2" t="n">
-        <v>-573.4700030041744</v>
+        <v>-680.3168839333244</v>
       </c>
       <c r="K2" t="n">
-        <v>-569.4920349110458</v>
+        <v>-676.4143964961615</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,77 +535,77 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3109215923320096</v>
+        <v>0.9556402219245705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002823068040077226</v>
+        <v>0.001020260575170568</v>
       </c>
       <c r="F3" t="n">
-        <v>2.899069230777581e-05</v>
+        <v>1.934551722391571e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005384300540253656</v>
+        <v>0.001390881634932165</v>
       </c>
       <c r="H3" t="n">
-        <v>308.2023884397309</v>
+        <v>253.0259911177112</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2077438157850126</v>
+        <v>0.01430928760883451</v>
       </c>
       <c r="J3" t="n">
-        <v>-560.2209296575531</v>
+        <v>-680.0930161694928</v>
       </c>
       <c r="K3" t="n">
-        <v>-556.2429615644246</v>
+        <v>-676.1905287323299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.0647247395407442</v>
+        <v>0.8452357203650596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005475839905176957</v>
+        <v>0.001625688661816989</v>
       </c>
       <c r="F4" t="n">
-        <v>4.479476787114006e-05</v>
+        <v>6.749346293468052e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006692889351478931</v>
+        <v>0.002597950402426507</v>
       </c>
       <c r="H4" t="n">
-        <v>1088.039139078064</v>
+        <v>718.1684751958898</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6418975563994662</v>
+        <v>0.04743400843288757</v>
       </c>
       <c r="J4" t="n">
-        <v>-534.724637553531</v>
+        <v>-615.1153749654534</v>
       </c>
       <c r="K4" t="n">
-        <v>-528.7576854138382</v>
+        <v>-611.2128875282905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,38 +613,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dVdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1288552148376154</v>
+        <v>0.7669122062593687</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003874259614073351</v>
+        <v>0.002147137349409636</v>
       </c>
       <c r="F5" t="n">
-        <v>4.749284526871076e-05</v>
+        <v>1.016507323554784e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006891505297735086</v>
+        <v>0.003188271198556961</v>
       </c>
       <c r="H5" t="n">
-        <v>1457.823911086033</v>
+        <v>768.133084329074</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6783796188859456</v>
+        <v>0.07043345367345427</v>
       </c>
       <c r="J5" t="n">
-        <v>-535.5663001463022</v>
+        <v>-595.8207511240803</v>
       </c>
       <c r="K5" t="n">
-        <v>-533.5773160997379</v>
+        <v>-593.8695074054989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,32 +652,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1288552148376154</v>
+        <v>0.7609669705809067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003874259614073351</v>
+        <v>0.002106357090616844</v>
       </c>
       <c r="F6" t="n">
-        <v>4.749284526871076e-05</v>
+        <v>1.042434788525947e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006891505297735086</v>
+        <v>0.003228675871817961</v>
       </c>
       <c r="H6" t="n">
-        <v>1457.823911086033</v>
+        <v>661.7891455696154</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6783796188859456</v>
+        <v>0.07221720586924768</v>
       </c>
       <c r="J6" t="n">
-        <v>-535.5663001463022</v>
+        <v>-594.5110499508493</v>
       </c>
       <c r="K6" t="n">
-        <v>-533.5773160997379</v>
+        <v>-592.5598062322679</v>
       </c>
     </row>
     <row r="7">
@@ -691,38 +691,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.1613771854246493</v>
+        <v>0.7125486346279917</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00406390988750481</v>
+        <v>0.0026214230249368</v>
       </c>
       <c r="F7" t="n">
-        <v>4.886109949354131e-05</v>
+        <v>1.253589531125814e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006990071494165228</v>
+        <v>0.003540606630403629</v>
       </c>
       <c r="H7" t="n">
-        <v>1590.227412921097</v>
+        <v>1508.305341324516</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6978947167940807</v>
+        <v>0.08674418473832039</v>
       </c>
       <c r="J7" t="n">
-        <v>-534.0325654303032</v>
+        <v>-584.9195490076752</v>
       </c>
       <c r="K7" t="n">
-        <v>-532.0435813837389</v>
+        <v>-582.9683052890938</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -730,110 +730,110 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, mu_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.3518201161660621</v>
+        <v>-0.1224738805835961</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003676107089678999</v>
+        <v>0.00630988724601267</v>
       </c>
       <c r="F8" t="n">
-        <v>5.687335520476002e-05</v>
+        <v>4.895163756974061e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007541442514848205</v>
+        <v>0.006996544687897063</v>
       </c>
       <c r="H8" t="n">
-        <v>877.6800461580765</v>
+        <v>4082.887148907911</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8131716923969241</v>
+        <v>0.6755528606427553</v>
       </c>
       <c r="J8" t="n">
-        <v>-523.8329144317564</v>
+        <v>-512.0832422522421</v>
       </c>
       <c r="K8" t="n">
-        <v>-519.8549463386279</v>
+        <v>-508.1807548150793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, I, V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.4201383808407051</v>
+        <v>-0.1316369384712319</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006024469998403748</v>
+        <v>0.006353599809321117</v>
       </c>
       <c r="F9" t="n">
-        <v>5.974761997368027e-05</v>
+        <v>4.935124302738645e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007729658464232444</v>
+        <v>0.007025043987576622</v>
       </c>
       <c r="H9" t="n">
-        <v>3291.357198646209</v>
+        <v>4093.623310953735</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8561666751723863</v>
+        <v>0.6810512548229777</v>
       </c>
       <c r="J9" t="n">
-        <v>-517.1705848552147</v>
+        <v>-511.6604754293395</v>
       </c>
       <c r="K9" t="n">
-        <v>-509.2146486689576</v>
+        <v>-507.7579879921767</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4720797138620128</v>
+        <v>-0.6632413224599427</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006267901696259799</v>
+        <v>0.008005224546376656</v>
       </c>
       <c r="F10" t="n">
-        <v>6.193287957102055e-05</v>
+        <v>7.253477146902001e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007869744568346583</v>
+        <v>0.008516734789167736</v>
       </c>
       <c r="H10" t="n">
-        <v>1287.834068632945</v>
+        <v>4651.338609079356</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8883345343486072</v>
+        <v>0.9990463421560224</v>
       </c>
       <c r="J10" t="n">
-        <v>-513.2308047328461</v>
+        <v>-493.6351142396589</v>
       </c>
       <c r="K10" t="n">
-        <v>-503.2858845000247</v>
+        <v>-491.6838705210775</v>
       </c>
     </row>
   </sheetData>
